--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N32_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0001T0006Z000C1N32_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>49.76137964356203</v>
+        <v>8.086224192078831</v>
       </c>
       <c r="D2" t="n">
-        <v>29.46113118601656</v>
+        <v>4.78743381772769</v>
       </c>
       <c r="E2" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F2" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>63.37034974619289</v>
+        <v>10.29768183375634</v>
       </c>
       <c r="D3" t="n">
-        <v>64.87030605036358</v>
+        <v>10.54142473318408</v>
       </c>
       <c r="E3" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F3" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.98586514336029</v>
+        <v>8.935203085796047</v>
       </c>
       <c r="D4" t="n">
-        <v>56.55872533737364</v>
+        <v>9.190792867323218</v>
       </c>
       <c r="E4" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F4" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>52.97634882329205</v>
+        <v>8.608656683784959</v>
       </c>
       <c r="D5" t="n">
-        <v>54.44364185397225</v>
+        <v>8.847091801270491</v>
       </c>
       <c r="E5" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F5" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>54.22473687627769</v>
+        <v>8.811519742395125</v>
       </c>
       <c r="D6" t="n">
-        <v>19.19826149536579</v>
+        <v>3.119717492996941</v>
       </c>
       <c r="E6" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F6" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.73325709636885</v>
+        <v>9.544154278159938</v>
       </c>
       <c r="D7" t="n">
-        <v>16.01849269534877</v>
+        <v>2.603005062994175</v>
       </c>
       <c r="E7" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F7" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.04000614363105</v>
+        <v>8.456500998340047</v>
       </c>
       <c r="D8" t="n">
-        <v>53.07536394571244</v>
+        <v>8.624746641178271</v>
       </c>
       <c r="E8" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F8" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>49.84830131396372</v>
+        <v>8.100348963519105</v>
       </c>
       <c r="D9" t="n">
-        <v>50.57743773261403</v>
+        <v>8.21883363154978</v>
       </c>
       <c r="E9" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F9" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>47.00886230144794</v>
+        <v>7.63894012398529</v>
       </c>
       <c r="D10" t="n">
-        <v>47.39996265344535</v>
+        <v>7.702493931184869</v>
       </c>
       <c r="E10" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F10" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>53.2505482907593</v>
+        <v>8.653214097248386</v>
       </c>
       <c r="D11" t="n">
-        <v>33.83597559468981</v>
+        <v>5.498346034137094</v>
       </c>
       <c r="E11" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F11" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.98603908799669</v>
+        <v>7.472731351799462</v>
       </c>
       <c r="D12" t="n">
-        <v>37.0258006140463</v>
+        <v>6.016692599782523</v>
       </c>
       <c r="E12" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F12" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>37.09260594982366</v>
+        <v>6.027548466846344</v>
       </c>
       <c r="D13" t="n">
-        <v>35.92526072689977</v>
+        <v>5.837854868121213</v>
       </c>
       <c r="E13" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F13" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>43.08973479757275</v>
+        <v>7.002081904605572</v>
       </c>
       <c r="D14" t="n">
-        <v>41.46936615192885</v>
+        <v>6.738771999688439</v>
       </c>
       <c r="E14" t="n">
-        <v>6.498841079111779</v>
+        <v>1.056061675355664</v>
       </c>
       <c r="F14" t="n">
-        <v>14.12337482393186</v>
+        <v>2.295048408888927</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
